--- a/TalentBaby/Activities.xlsx
+++ b/TalentBaby/Activities.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Github\Mobile\Mobile-App\TalentBaby\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6609C5E6-F192-42A0-8C00-E855F93B0A34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E381028-86ED-42BA-8B84-0E34EEFAC617}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="1125" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="143">
   <si>
     <t>Month</t>
   </si>
@@ -295,16 +295,188 @@
   </si>
   <si>
     <t>Favourite Moment</t>
+  </si>
+  <si>
+    <t>Concept Of Length</t>
+  </si>
+  <si>
+    <t>Building Structures 3</t>
+  </si>
+  <si>
+    <t>Arrange In Order</t>
+  </si>
+  <si>
+    <t>Folding Paper</t>
+  </si>
+  <si>
+    <t>Drawing L3</t>
+  </si>
+  <si>
+    <t>Spot Difference</t>
+  </si>
+  <si>
+    <t>Machine Functions</t>
+  </si>
+  <si>
+    <t>Taking Turns 3</t>
+  </si>
+  <si>
+    <t>Draw Stick Figure</t>
+  </si>
+  <si>
+    <t>Playing with colors</t>
+  </si>
+  <si>
+    <t>Feel A Shape</t>
+  </si>
+  <si>
+    <t>Dinosaur Excavation</t>
+  </si>
+  <si>
+    <t>Group Reading</t>
+  </si>
+  <si>
+    <t>Shapes From Objects</t>
+  </si>
+  <si>
+    <t>Clip Fun</t>
+  </si>
+  <si>
+    <t>Everyday Counting</t>
+  </si>
+  <si>
+    <t>Puddles &amp; Stones</t>
+  </si>
+  <si>
+    <t>Creative Art - Flower Pot</t>
+  </si>
+  <si>
+    <t>Pools &amp; Boats</t>
+  </si>
+  <si>
+    <t>Finding Numbers</t>
+  </si>
+  <si>
+    <t>Visit To Bookstore</t>
+  </si>
+  <si>
+    <t>Painting &amp; Textures</t>
+  </si>
+  <si>
+    <t>Visual Scanning Fun</t>
+  </si>
+  <si>
+    <t>Sand &amp; Light Art</t>
+  </si>
+  <si>
+    <t>Spot The Difference</t>
+  </si>
+  <si>
+    <t>Catch The Ball L3</t>
+  </si>
+  <si>
+    <t>Fine Motor</t>
+  </si>
+  <si>
+    <t>Fork and Sponge Painting</t>
+  </si>
+  <si>
+    <t>Finger Dexterity</t>
+  </si>
+  <si>
+    <t>Hopscotch Games</t>
+  </si>
+  <si>
+    <t>Gross Motor</t>
+  </si>
+  <si>
+    <t>Painting By Blowing Air</t>
+  </si>
+  <si>
+    <t>Muscle development</t>
+  </si>
+  <si>
+    <t>Sensory Development</t>
+  </si>
+  <si>
+    <t>Concept Learning</t>
+  </si>
+  <si>
+    <t>Problem Solving</t>
+  </si>
+  <si>
+    <t>Memory and Attention</t>
+  </si>
+  <si>
+    <t>Color &amp; Number</t>
+  </si>
+  <si>
+    <t>Early Knowledge</t>
+  </si>
+  <si>
+    <t>Memory Game</t>
+  </si>
+  <si>
+    <t>Articulation &amp; Reasoning</t>
+  </si>
+  <si>
+    <t>Colour &amp; Size</t>
+  </si>
+  <si>
+    <t>Mathematical Judgement 1</t>
+  </si>
+  <si>
+    <t>Nurturing Creativity</t>
+  </si>
+  <si>
+    <t>Bring Books to Life 1</t>
+  </si>
+  <si>
+    <t>Thinking Expansion</t>
+  </si>
+  <si>
+    <t>Left-Right Brain Coordination</t>
+  </si>
+  <si>
+    <t>Imagination</t>
+  </si>
+  <si>
+    <t>Matching Items</t>
+  </si>
+  <si>
+    <t>Recap Of The Day</t>
+  </si>
+  <si>
+    <t>Color Tag</t>
+  </si>
+  <si>
+    <t>Storybook Play</t>
+  </si>
+  <si>
+    <t>Language Comprehension</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -330,8 +502,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -612,12 +787,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B3:E93"/>
+  <dimension ref="B3:E225"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="6.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15.140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="25.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3" spans="2:5" x14ac:dyDescent="0.25">
@@ -1134,6 +1310,816 @@
       <c r="C93" t="s">
         <v>4</v>
       </c>
+      <c r="D93" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="94" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="D94" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="95" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="D95" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="96" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="D96" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="97" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D97" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="98" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D98" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="99" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D99" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="100" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D100" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="101" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D101" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="102" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D102" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="103" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D103" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="104" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D104" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="105" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D105" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="106" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D106" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="107" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D107" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="108" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D108" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="109" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D109" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="110" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D110" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="111" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D111" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="112" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D112" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="113" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D113" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="114" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D114" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="115" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D115" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="116" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D116" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="117" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D117" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="118" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D118" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="119" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D119" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="120" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D120" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="121" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D121" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="122" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D122" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="123" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D123" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="124" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D124" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="125" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D125" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="126" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D126" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="127" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D127" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="128" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D128" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="129" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="D129" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="130" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="D130" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="131" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="D131" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="132" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="D132" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="133" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="D133" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="134" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C134" t="s">
+        <v>15</v>
+      </c>
+      <c r="D134" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="135" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="D135" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="136" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="D136" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="137" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="D137" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="138" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="D138" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="139" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="D139" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="140" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="D140" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="141" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="D141" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="142" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="D142" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="143" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="D143" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="144" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="D144" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="145" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D145" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="146" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D146" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="147" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D147" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="148" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D148" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="149" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D149" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="150" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D150" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="151" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D151" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="152" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D152" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="153" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D153" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="154" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D154" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="155" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D155" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="156" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D156" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="157" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D157" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="158" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D158" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="159" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D159" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="160" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D160" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="161" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="D161" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="162" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="D162" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="163" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="D163" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="164" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="D164" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="165" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="D165" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="166" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="D166" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="167" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="D167" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="168" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="D168" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="169" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C169" t="s">
+        <v>42</v>
+      </c>
+      <c r="D169" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="170" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="D170" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="171" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="D171" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="172" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="D172" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="173" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="D173" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="174" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C174" t="s">
+        <v>38</v>
+      </c>
+      <c r="D174" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="175" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="D175" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="176" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="D176" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="177" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="D177" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="178" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="D178" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="179" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="D179" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="180" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="D180" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="181" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="D181" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="182" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="D182" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="183" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B183">
+        <v>32</v>
+      </c>
+      <c r="C183" t="s">
+        <v>4</v>
+      </c>
+      <c r="D183" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="184" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="D184" t="s">
+        <v>115</v>
+      </c>
+      <c r="E184" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="185" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="D185" t="s">
+        <v>117</v>
+      </c>
+      <c r="E185" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="186" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="D186" t="s">
+        <v>98</v>
+      </c>
+      <c r="E186" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="187" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="D187" t="s">
+        <v>119</v>
+      </c>
+      <c r="E187" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="188" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="D188" t="s">
+        <v>121</v>
+      </c>
+      <c r="E188" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="189" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="D189" t="s">
+        <v>75</v>
+      </c>
+      <c r="E189" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="190" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="D190" t="s">
+        <v>108</v>
+      </c>
+      <c r="E190" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="191" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="D191" t="s">
+        <v>111</v>
+      </c>
+      <c r="E191" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="192" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="C192" t="s">
+        <v>15</v>
+      </c>
+      <c r="D192" t="s">
+        <v>90</v>
+      </c>
+      <c r="E192" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="193" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D193" t="s">
+        <v>91</v>
+      </c>
+      <c r="E193" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="194" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D194" t="s">
+        <v>92</v>
+      </c>
+      <c r="E194" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="195" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D195" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="E195" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="196" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D196" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="E196" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="197" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D197" t="s">
+        <v>76</v>
+      </c>
+      <c r="E197" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="198" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D198" t="s">
+        <v>114</v>
+      </c>
+      <c r="E198" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="199" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D199" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="E199" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="200" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D200" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E200" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="201" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D201" t="s">
+        <v>77</v>
+      </c>
+      <c r="E201" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="202" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D202" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="E202" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="203" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D203" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="E203" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="204" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D204" t="s">
+        <v>79</v>
+      </c>
+      <c r="E204" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="205" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D205" t="s">
+        <v>26</v>
+      </c>
+      <c r="E205" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="206" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D206" t="s">
+        <v>99</v>
+      </c>
+      <c r="E206" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="207" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D207" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="E207" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="208" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D208" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="E208" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="209" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D209" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="E209" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="210" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D210" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="E210" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="211" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D211" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="E211" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="212" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D212" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="E212" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="213" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D213" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="E213" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="214" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D214" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="E214" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="215" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D215" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="E215" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="216" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D216" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="E216" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="217" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D217" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="E217" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="218" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D218" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="E218" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="219" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D219" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="E219" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="220" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D220" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="E220" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="221" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D221" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="E221" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="222" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D222" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="E222" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="223" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D223" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="E223" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="224" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D224" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="E224" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="225" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C225" t="s">
+        <v>42</v>
+      </c>
+      <c r="D225" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="E225" t="s">
+        <v>142</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
